--- a/artfynd/A 22153-2026 artfynd.xlsx
+++ b/artfynd/A 22153-2026 artfynd.xlsx
@@ -4139,10 +4139,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134021376</v>
+        <v>134021415</v>
       </c>
       <c r="B34" t="n">
-        <v>79117</v>
+        <v>79025</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4150,21 +4150,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>396153</v>
+        <v>396064</v>
       </c>
       <c r="R34" t="n">
-        <v>6804395</v>
+        <v>6804542</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4246,10 +4246,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134021415</v>
+        <v>134021376</v>
       </c>
       <c r="B35" t="n">
-        <v>79025</v>
+        <v>79117</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4257,21 +4257,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4281,10 +4281,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>396064</v>
+        <v>396153</v>
       </c>
       <c r="R35" t="n">
-        <v>6804542</v>
+        <v>6804395</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4316,7 +4316,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4679,10 +4679,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134021397</v>
+        <v>134021416</v>
       </c>
       <c r="B39" t="n">
-        <v>78762</v>
+        <v>92421</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4690,21 +4690,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6437</v>
+        <v>5467</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4714,10 +4714,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>396051</v>
+        <v>396064</v>
       </c>
       <c r="R39" t="n">
-        <v>6804389</v>
+        <v>6804542</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4786,10 +4786,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134021416</v>
+        <v>134021388</v>
       </c>
       <c r="B40" t="n">
-        <v>92421</v>
+        <v>79978</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4797,21 +4797,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5467</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>396064</v>
+        <v>396143</v>
       </c>
       <c r="R40" t="n">
-        <v>6804542</v>
+        <v>6804329</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4893,7 +4893,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134021388</v>
+        <v>134021409</v>
       </c>
       <c r="B41" t="n">
         <v>79978</v>
@@ -4928,10 +4928,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>396143</v>
+        <v>396053</v>
       </c>
       <c r="R41" t="n">
-        <v>6804329</v>
+        <v>6804513</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5000,10 +5000,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134021409</v>
+        <v>134021397</v>
       </c>
       <c r="B42" t="n">
-        <v>79978</v>
+        <v>78762</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5011,21 +5011,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>396053</v>
+        <v>396051</v>
       </c>
       <c r="R42" t="n">
-        <v>6804513</v>
+        <v>6804389</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 22153-2026 artfynd.xlsx
+++ b/artfynd/A 22153-2026 artfynd.xlsx
@@ -3928,7 +3928,7 @@
         <v>134021395</v>
       </c>
       <c r="B32" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>134021410</v>
       </c>
       <c r="B33" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>134021415</v>
       </c>
       <c r="B34" t="n">
-        <v>79025</v>
+        <v>79032</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>134021376</v>
       </c>
       <c r="B35" t="n">
-        <v>79117</v>
+        <v>79124</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4465,10 +4465,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134021390</v>
+        <v>134021378</v>
       </c>
       <c r="B37" t="n">
-        <v>79025</v>
+        <v>79956</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4476,21 +4476,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4503,7 +4503,7 @@
         <v>396151</v>
       </c>
       <c r="R37" t="n">
-        <v>6804323</v>
+        <v>6804393</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4572,10 +4572,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134021378</v>
+        <v>134021390</v>
       </c>
       <c r="B38" t="n">
-        <v>79949</v>
+        <v>79032</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4583,21 +4583,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4610,7 +4610,7 @@
         <v>396151</v>
       </c>
       <c r="R38" t="n">
-        <v>6804393</v>
+        <v>6804323</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4679,10 +4679,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134021416</v>
+        <v>134021409</v>
       </c>
       <c r="B39" t="n">
-        <v>92421</v>
+        <v>79985</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4690,21 +4690,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5467</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4714,10 +4714,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>396064</v>
+        <v>396053</v>
       </c>
       <c r="R39" t="n">
-        <v>6804542</v>
+        <v>6804513</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4786,10 +4786,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134021388</v>
+        <v>134021397</v>
       </c>
       <c r="B40" t="n">
-        <v>79978</v>
+        <v>78769</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4797,21 +4797,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>396143</v>
+        <v>396051</v>
       </c>
       <c r="R40" t="n">
-        <v>6804329</v>
+        <v>6804389</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4893,10 +4893,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134021409</v>
+        <v>134021416</v>
       </c>
       <c r="B41" t="n">
-        <v>79978</v>
+        <v>92428</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4904,21 +4904,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>5467</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4928,10 +4928,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>396053</v>
+        <v>396064</v>
       </c>
       <c r="R41" t="n">
-        <v>6804513</v>
+        <v>6804542</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5000,10 +5000,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134021397</v>
+        <v>134021388</v>
       </c>
       <c r="B42" t="n">
-        <v>78762</v>
+        <v>79985</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5011,21 +5011,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>396051</v>
+        <v>396143</v>
       </c>
       <c r="R42" t="n">
-        <v>6804389</v>
+        <v>6804329</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5107,10 +5107,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134021387</v>
+        <v>134021414</v>
       </c>
       <c r="B43" t="n">
-        <v>79978</v>
+        <v>79124</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5118,21 +5118,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5142,10 +5142,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>396151</v>
+        <v>396059</v>
       </c>
       <c r="R43" t="n">
-        <v>6804323</v>
+        <v>6804529</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5177,7 +5177,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5214,10 +5214,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134021414</v>
+        <v>134021387</v>
       </c>
       <c r="B44" t="n">
-        <v>79117</v>
+        <v>79985</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5225,21 +5225,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5249,10 +5249,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>396059</v>
+        <v>396151</v>
       </c>
       <c r="R44" t="n">
-        <v>6804529</v>
+        <v>6804323</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5324,7 +5324,7 @@
         <v>134021384</v>
       </c>
       <c r="B45" t="n">
-        <v>92139</v>
+        <v>92146</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>134021375</v>
       </c>
       <c r="B46" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         <v>134021385</v>
       </c>
       <c r="B47" t="n">
-        <v>79025</v>
+        <v>79032</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5642,10 +5642,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134021412</v>
+        <v>134021399</v>
       </c>
       <c r="B48" t="n">
-        <v>79978</v>
+        <v>79124</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5653,21 +5653,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5677,10 +5677,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>396064</v>
+        <v>396034</v>
       </c>
       <c r="R48" t="n">
-        <v>6804542</v>
+        <v>6804390</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5712,7 +5712,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5749,10 +5749,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134021399</v>
+        <v>134021412</v>
       </c>
       <c r="B49" t="n">
-        <v>79117</v>
+        <v>79985</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5760,21 +5760,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>396034</v>
+        <v>396064</v>
       </c>
       <c r="R49" t="n">
-        <v>6804390</v>
+        <v>6804542</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5819,7 +5819,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5859,7 +5859,7 @@
         <v>134021391</v>
       </c>
       <c r="B50" t="n">
-        <v>79025</v>
+        <v>79032</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 22153-2026 artfynd.xlsx
+++ b/artfynd/A 22153-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131033342</v>
+        <v>131033283</v>
       </c>
       <c r="B2" t="n">
-        <v>79249</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>395753</v>
+        <v>395745</v>
       </c>
       <c r="R2" t="n">
-        <v>6804557</v>
+        <v>6804404</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131033283</v>
+        <v>131033362</v>
       </c>
       <c r="B3" t="n">
-        <v>79281</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>395745</v>
+        <v>395883</v>
       </c>
       <c r="R3" t="n">
-        <v>6804404</v>
+        <v>6804433</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131033348</v>
+        <v>134021385</v>
       </c>
       <c r="B4" t="n">
-        <v>79249</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Älgforsen, norr om, Dlr</t>
+          <t>Älgforsen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>395756</v>
+        <v>396171</v>
       </c>
       <c r="R4" t="n">
-        <v>6804343</v>
+        <v>6804332</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,22 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131033331</v>
+        <v>134021390</v>
       </c>
       <c r="B5" t="n">
-        <v>79249</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,34 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Älgforsen, norr om, Dlr</t>
+          <t>Älgforsen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>395707</v>
+        <v>396151</v>
       </c>
       <c r="R5" t="n">
-        <v>6804307</v>
+        <v>6804323</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131033344</v>
+        <v>134021391</v>
       </c>
       <c r="B6" t="n">
-        <v>79249</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,34 +1114,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Älgforsen, norr om, Dlr</t>
+          <t>Älgforsen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>395753</v>
+        <v>396143</v>
       </c>
       <c r="R6" t="n">
-        <v>6804482</v>
+        <v>6804329</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,22 +1168,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131033302</v>
+        <v>134021415</v>
       </c>
       <c r="B7" t="n">
-        <v>79007</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,34 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Älgforsen, norr om, Dlr</t>
+          <t>Älgforsen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>395679</v>
+        <v>396064</v>
       </c>
       <c r="R7" t="n">
-        <v>6804524</v>
+        <v>6804542</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,22 +1275,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131033324</v>
+        <v>131033308</v>
       </c>
       <c r="B8" t="n">
-        <v>79249</v>
+        <v>81312</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>395676</v>
+        <v>395881</v>
       </c>
       <c r="R8" t="n">
-        <v>6804490</v>
+        <v>6804325</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,50 +1424,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131033294</v>
+        <v>134021384</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>92153</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Älgforsen, norr om, Dlr</t>
+          <t>Älgforsen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>395714</v>
+        <v>396171</v>
       </c>
       <c r="R9" t="n">
-        <v>6804552</v>
+        <v>6804332</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,27 +1489,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,45 +1531,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131033347</v>
+        <v>134021407</v>
       </c>
       <c r="B10" t="n">
-        <v>79249</v>
+        <v>96410</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2812</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Älgforsen, norr om, Dlr</t>
+          <t>Älgforsen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>395745</v>
+        <v>396062</v>
       </c>
       <c r="R10" t="n">
-        <v>6804404</v>
+        <v>6804434</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,22 +1596,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131033346</v>
+        <v>134021416</v>
       </c>
       <c r="B11" t="n">
-        <v>79249</v>
+        <v>92435</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1659,34 +1649,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5467</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Älgforsen, norr om, Dlr</t>
+          <t>Älgforsen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>395744</v>
+        <v>396064</v>
       </c>
       <c r="R11" t="n">
-        <v>6804417</v>
+        <v>6804542</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,22 +1703,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,50 +1745,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131033288</v>
+        <v>131033321</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>395651</v>
+        <v>395718</v>
       </c>
       <c r="R12" t="n">
-        <v>6804457</v>
+        <v>6804573</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1840,12 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,14 +1852,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131033334</v>
+        <v>131033322</v>
       </c>
       <c r="B13" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1907,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>395718</v>
+        <v>395692</v>
       </c>
       <c r="R13" t="n">
-        <v>6804558</v>
+        <v>6804550</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1942,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1952,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1979,14 +1959,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131033352</v>
+        <v>131033323</v>
       </c>
       <c r="B14" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2014,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>395857</v>
+        <v>395680</v>
       </c>
       <c r="R14" t="n">
-        <v>6804292</v>
+        <v>6804541</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2049,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2059,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,14 +2066,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131033323</v>
+        <v>131033324</v>
       </c>
       <c r="B15" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2121,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>395680</v>
+        <v>395676</v>
       </c>
       <c r="R15" t="n">
-        <v>6804541</v>
+        <v>6804490</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2166,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,14 +2173,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131033321</v>
+        <v>131033325</v>
       </c>
       <c r="B16" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2228,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>395718</v>
+        <v>395696</v>
       </c>
       <c r="R16" t="n">
-        <v>6804573</v>
+        <v>6804471</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2273,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2303,11 +2283,11 @@
         <v>131033326</v>
       </c>
       <c r="B17" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2410,11 +2390,11 @@
         <v>131033327</v>
       </c>
       <c r="B18" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2514,32 +2494,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131033299</v>
+        <v>131033328</v>
       </c>
       <c r="B19" t="n">
-        <v>79273</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2549,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>395890</v>
+        <v>395711</v>
       </c>
       <c r="R19" t="n">
-        <v>6804464</v>
+        <v>6804347</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2594,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2621,50 +2601,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131033295</v>
+        <v>131033329</v>
       </c>
       <c r="B20" t="n">
-        <v>57887</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>395744</v>
+        <v>395716</v>
       </c>
       <c r="R20" t="n">
-        <v>6804575</v>
+        <v>6804338</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2696,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2706,12 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2738,14 +2708,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131033353</v>
+        <v>131033330</v>
       </c>
       <c r="B21" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2773,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>395859</v>
+        <v>395702</v>
       </c>
       <c r="R21" t="n">
-        <v>6804312</v>
+        <v>6804325</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2808,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2818,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2845,32 +2815,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131033303</v>
+        <v>131033331</v>
       </c>
       <c r="B22" t="n">
-        <v>79007</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2880,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>395706</v>
+        <v>395707</v>
       </c>
       <c r="R22" t="n">
-        <v>6804535</v>
+        <v>6804307</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2915,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2925,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2952,14 +2922,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131033330</v>
+        <v>131033332</v>
       </c>
       <c r="B23" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2987,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>395702</v>
+        <v>395641</v>
       </c>
       <c r="R23" t="n">
-        <v>6804325</v>
+        <v>6804509</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3022,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3032,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3059,14 +3029,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131033322</v>
+        <v>131033333</v>
       </c>
       <c r="B24" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3094,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>395692</v>
+        <v>395717</v>
       </c>
       <c r="R24" t="n">
-        <v>6804550</v>
+        <v>6804542</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3129,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3139,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3166,14 +3136,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131033333</v>
+        <v>131033334</v>
       </c>
       <c r="B25" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3201,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>395717</v>
+        <v>395718</v>
       </c>
       <c r="R25" t="n">
-        <v>6804542</v>
+        <v>6804558</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3236,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3246,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3273,50 +3243,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131033293</v>
+        <v>131033340</v>
       </c>
       <c r="B26" t="n">
-        <v>57887</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>395668</v>
+        <v>395817</v>
       </c>
       <c r="R26" t="n">
-        <v>6804432</v>
+        <v>6804597</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3348,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3358,12 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3390,14 +3350,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131033345</v>
+        <v>131033341</v>
       </c>
       <c r="B27" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3425,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>395748</v>
+        <v>395797</v>
       </c>
       <c r="R27" t="n">
-        <v>6804429</v>
+        <v>6804591</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3460,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3470,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3497,32 +3457,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131033362</v>
+        <v>131033342</v>
       </c>
       <c r="B28" t="n">
-        <v>78915</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3532,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>395883</v>
+        <v>395753</v>
       </c>
       <c r="R28" t="n">
-        <v>6804433</v>
+        <v>6804557</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3567,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3577,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3604,14 +3564,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131033332</v>
+        <v>131033344</v>
       </c>
       <c r="B29" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3639,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>395641</v>
+        <v>395753</v>
       </c>
       <c r="R29" t="n">
-        <v>6804509</v>
+        <v>6804482</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3674,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3684,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3711,14 +3671,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131033349</v>
+        <v>131033345</v>
       </c>
       <c r="B30" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3746,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>395757</v>
+        <v>395748</v>
       </c>
       <c r="R30" t="n">
-        <v>6804291</v>
+        <v>6804429</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3781,7 +3741,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3791,7 +3751,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3818,14 +3778,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131033341</v>
+        <v>131033346</v>
       </c>
       <c r="B31" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3853,10 +3813,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>395797</v>
+        <v>395744</v>
       </c>
       <c r="R31" t="n">
-        <v>6804591</v>
+        <v>6804417</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3888,7 +3848,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3898,7 +3858,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3925,45 +3885,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134021395</v>
+        <v>131033347</v>
       </c>
       <c r="B32" t="n">
-        <v>79985</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Älgforsen, Dlr</t>
+          <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>396055</v>
+        <v>395745</v>
       </c>
       <c r="R32" t="n">
-        <v>6804382</v>
+        <v>6804404</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3990,22 +3950,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4032,14 +3992,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134021410</v>
+        <v>131033348</v>
       </c>
       <c r="B33" t="n">
-        <v>79366</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4063,14 +4023,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Älgforsen, Dlr</t>
+          <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>396045</v>
+        <v>395756</v>
       </c>
       <c r="R33" t="n">
-        <v>6804496</v>
+        <v>6804343</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4097,22 +4057,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4139,45 +4099,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134021415</v>
+        <v>131033349</v>
       </c>
       <c r="B34" t="n">
-        <v>79032</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Älgforsen, Dlr</t>
+          <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>396064</v>
+        <v>395757</v>
       </c>
       <c r="R34" t="n">
-        <v>6804542</v>
+        <v>6804291</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4204,22 +4164,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4246,45 +4206,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134021376</v>
+        <v>131033350</v>
       </c>
       <c r="B35" t="n">
-        <v>79124</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Älgforsen, Dlr</t>
+          <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>396153</v>
+        <v>395801</v>
       </c>
       <c r="R35" t="n">
-        <v>6804395</v>
+        <v>6804274</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4311,22 +4271,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4353,50 +4313,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134021393</v>
+        <v>131033352</v>
       </c>
       <c r="B36" t="n">
-        <v>57796</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102976</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Älgforsen, Dlr</t>
+          <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>396143</v>
+        <v>395857</v>
       </c>
       <c r="R36" t="n">
-        <v>6804329</v>
+        <v>6804292</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4423,22 +4378,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4465,45 +4420,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134021378</v>
+        <v>131033353</v>
       </c>
       <c r="B37" t="n">
-        <v>79956</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Älgforsen, Dlr</t>
+          <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>396151</v>
+        <v>395859</v>
       </c>
       <c r="R37" t="n">
-        <v>6804393</v>
+        <v>6804312</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4530,22 +4485,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4572,32 +4527,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134021390</v>
+        <v>134021410</v>
       </c>
       <c r="B38" t="n">
-        <v>79032</v>
+        <v>79373</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4607,10 +4562,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>396151</v>
+        <v>396045</v>
       </c>
       <c r="R38" t="n">
-        <v>6804323</v>
+        <v>6804496</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4642,7 +4597,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4652,7 +4607,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4679,45 +4634,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134021409</v>
+        <v>131033299</v>
       </c>
       <c r="B39" t="n">
-        <v>79985</v>
+        <v>79351</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Älgforsen, Dlr</t>
+          <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>396053</v>
+        <v>395890</v>
       </c>
       <c r="R39" t="n">
-        <v>6804513</v>
+        <v>6804464</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4744,22 +4699,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4789,7 +4744,7 @@
         <v>134021397</v>
       </c>
       <c r="B40" t="n">
-        <v>78769</v>
+        <v>78776</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4893,10 +4848,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134021416</v>
+        <v>131033309</v>
       </c>
       <c r="B41" t="n">
-        <v>92428</v>
+        <v>79084</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4904,34 +4859,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5467</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Älgforsen, Dlr</t>
+          <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>396064</v>
+        <v>395969</v>
       </c>
       <c r="R41" t="n">
-        <v>6804542</v>
+        <v>6804420</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4958,22 +4913,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5000,10 +4955,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134021388</v>
+        <v>131033282</v>
       </c>
       <c r="B42" t="n">
-        <v>79985</v>
+        <v>79946</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5031,14 +4986,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Älgforsen, Dlr</t>
+          <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>396143</v>
+        <v>395972</v>
       </c>
       <c r="R42" t="n">
-        <v>6804329</v>
+        <v>6804416</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5065,22 +5020,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5107,10 +5062,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134021414</v>
+        <v>134021375</v>
       </c>
       <c r="B43" t="n">
-        <v>79124</v>
+        <v>79992</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5118,21 +5073,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5142,10 +5097,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>396059</v>
+        <v>396158</v>
       </c>
       <c r="R43" t="n">
-        <v>6804529</v>
+        <v>6804418</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5177,7 +5132,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5187,7 +5142,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5217,7 +5172,7 @@
         <v>134021387</v>
       </c>
       <c r="B44" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5321,32 +5276,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134021384</v>
+        <v>134021388</v>
       </c>
       <c r="B45" t="n">
-        <v>92146</v>
+        <v>79992</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5356,10 +5311,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>396171</v>
+        <v>396143</v>
       </c>
       <c r="R45" t="n">
-        <v>6804332</v>
+        <v>6804329</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5391,7 +5346,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5401,7 +5356,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5428,10 +5383,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134021375</v>
+        <v>134021395</v>
       </c>
       <c r="B46" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5463,10 +5418,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>396158</v>
+        <v>396055</v>
       </c>
       <c r="R46" t="n">
-        <v>6804418</v>
+        <v>6804382</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5498,7 +5453,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5508,7 +5463,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5535,10 +5490,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134021385</v>
+        <v>134021409</v>
       </c>
       <c r="B47" t="n">
-        <v>79032</v>
+        <v>79992</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5546,21 +5501,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5570,10 +5525,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>396171</v>
+        <v>396053</v>
       </c>
       <c r="R47" t="n">
-        <v>6804332</v>
+        <v>6804513</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5605,7 +5560,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5615,7 +5570,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5642,10 +5597,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134021399</v>
+        <v>134021412</v>
       </c>
       <c r="B48" t="n">
-        <v>79124</v>
+        <v>79992</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5653,21 +5608,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5677,10 +5632,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>396034</v>
+        <v>396064</v>
       </c>
       <c r="R48" t="n">
-        <v>6804390</v>
+        <v>6804542</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5712,7 +5667,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5722,7 +5677,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5749,45 +5704,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134021412</v>
+        <v>131033287</v>
       </c>
       <c r="B49" t="n">
-        <v>79985</v>
+        <v>57950</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Älgforsen, Dlr</t>
+          <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>396064</v>
+        <v>395655</v>
       </c>
       <c r="R49" t="n">
-        <v>6804542</v>
+        <v>6804357</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5814,22 +5774,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5856,10 +5816,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134021391</v>
+        <v>131033288</v>
       </c>
       <c r="B50" t="n">
-        <v>79032</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5867,34 +5827,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Älgforsen, Dlr</t>
+          <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>396143</v>
+        <v>395651</v>
       </c>
       <c r="R50" t="n">
-        <v>6804329</v>
+        <v>6804457</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5921,22 +5886,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5960,6 +5930,2124 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>131033291</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Älgforsen, norr om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>395693</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6804282</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>131033292</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Älgforsen, norr om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>395697</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6804508</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>131033293</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Älgforsen, norr om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>395668</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6804432</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>131033294</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Älgforsen, norr om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>395714</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6804552</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>131033295</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Älgforsen, norr om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>395744</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6804575</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>131033297</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Älgforsen, norr om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>395970</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6804419</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>131033298</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Älgforsen, norr om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>395968</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6804424</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färska ringhack på nyligen bandad gran</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>131033358</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Älgforsen, norr om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>395749</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6804605</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Troliga färska spår efter födosökande tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>134021393</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57796</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>102976</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tornseglare</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Apus apus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Älgforsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>396143</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6804329</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>134021404</v>
+      </c>
+      <c r="B60" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Älgforsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>396063</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6804438</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>131033302</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Älgforsen, norr om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>395679</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6804524</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>131033303</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Älgforsen, norr om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>395706</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6804535</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>131033305</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Älgforsen, norr om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>395972</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6804417</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>134021376</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Älgforsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>396153</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6804395</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>134021382</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Älgforsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>396180</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6804366</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>134021399</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Älgforsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>396034</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6804390</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>134021414</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Älgforsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>396059</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6804529</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>134021378</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Älgforsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>396151</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6804393</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>131033285</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Älgforsen, norr om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>395763</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6804494</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22153-2026 artfynd.xlsx
+++ b/artfynd/A 22153-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AZ69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033283</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033362</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134021385</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134021390</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134021391</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134021415</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033308</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134021384</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134021407</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134021416</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033321</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033322</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033323</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033324</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033325</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2384,6 +2464,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033326</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2491,6 +2576,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033327</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2598,6 +2688,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033328</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2705,6 +2800,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033329</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2812,6 +2912,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033330</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2919,6 +3024,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033331</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3026,6 +3136,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033332</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3133,6 +3248,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033333</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3240,6 +3360,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033334</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3347,6 +3472,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033340</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3454,6 +3584,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033341</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3561,6 +3696,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033342</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3668,6 +3808,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033344</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3775,6 +3920,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033345</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3882,6 +4032,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033346</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3989,6 +4144,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033347</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4096,6 +4256,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033348</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4203,6 +4368,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033349</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4310,6 +4480,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033350</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4417,6 +4592,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033352</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4524,6 +4704,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033353</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4631,6 +4816,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134021410</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4738,6 +4928,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033299</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4845,6 +5040,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134021397</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4952,6 +5152,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033309</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5059,6 +5264,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033282</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5166,6 +5376,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134021375</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5273,6 +5488,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134021387</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5380,6 +5600,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134021388</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5487,6 +5712,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134021395</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5594,6 +5824,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134021409</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5701,6 +5936,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134021412</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5813,6 +6053,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033287</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5930,6 +6175,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033288</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6047,6 +6297,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033291</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6164,6 +6419,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033292</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6281,6 +6541,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033293</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6398,6 +6663,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033294</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6515,6 +6785,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033295</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6632,6 +6907,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033297</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6749,6 +7029,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033298</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6866,6 +7151,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033358</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6978,6 +7268,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134021393</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7085,6 +7380,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134021404</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7192,6 +7492,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033302</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7299,6 +7604,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033303</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7406,6 +7716,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033305</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7513,6 +7828,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134021376</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7620,6 +7940,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134021382</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7727,6 +8052,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134021399</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7834,6 +8164,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134021414</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7941,6 +8276,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134021378</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8048,8 +8388,83 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033285</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>